--- a/study/ordine_soggetti.xlsx
+++ b/study/ordine_soggetti.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,7 @@
         <v>80</v>
       </c>
       <c r="I4" t="n">
-        <v>57.14285714285714</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -1226,7 +1226,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
@@ -1272,7 +1272,7 @@
         <v>41.66666666666667</v>
       </c>
       <c r="I18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
@@ -1318,7 +1318,7 @@
         <v>58.33333333333334</v>
       </c>
       <c r="I19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J19" t="n">
         <v>2</v>
@@ -1821,7 +1821,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1855,58 +1855,68 @@
         </is>
       </c>
       <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
+      <c r="I31" s="2" t="n">
+        <v>90</v>
+      </c>
       <c r="J31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>IT?</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>presunto (nessun gaze, solo disegno)</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>mattina</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>fra</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>10:17 anguille/images@fra -&gt; 10:25 orso/text@fra</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="I32" t="n">
+        <v>80</v>
+      </c>
+      <c r="J32" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1931,14 +1941,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10:17 anguille/images@fra -&gt; 10:25 orso/text@fra</t>
+          <t>10:35 delfino/images@fra -&gt; 10:43 panda/text@fra</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>64.28571428571429</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="I33" t="n">
-        <v>80</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="J33" t="n">
         <v>2</v>
@@ -1947,7 +1957,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1977,123 +1987,123 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10:35 delfino/images@fra -&gt; 10:43 panda/text@fra</t>
+          <t>10:31 delfino/images@fra -&gt; 10:40 panda/text@fra</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>92.85714285714286</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="I34" t="n">
-        <v>78.57142857142857</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>IT?</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>presunto (1 gaze mancante)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>mattina</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>bene</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>11:20 tappeto/text@bene</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>mattina</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>mattina</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>fra</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>10:31 delfino/images@fra -&gt; 10:40 panda/text@fra</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="I35" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>F10</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>IT?</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>presunto (1 gaze mancante)</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>mattina</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>bene</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>11:20 tappeto/text@bene</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>11:04 volpe e bo/images@fra -&gt; 11:19 tappeto/text@fra</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>90</v>
+      </c>
+      <c r="J36" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2108,19 +2118,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>fra</t>
+          <t>bene/fra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11:04 volpe e bo/images@fra -&gt; 11:19 tappeto/text@fra</t>
+          <t>11:04 gatta/text@bene -&gt; 11:16 sbadiglio/images@fra</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="I37" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J37" t="n">
         <v>2</v>
@@ -2129,17 +2139,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2159,14 +2169,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11:04 gatta/text@bene -&gt; 11:16 sbadiglio/images@fra</t>
+          <t>11:08 volpe e bo/images@bene -&gt; 11:23 tappeto/text@fra</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>66.66666666666666</v>
+        <v>90</v>
       </c>
       <c r="I38" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J38" t="n">
         <v>2</v>
@@ -2175,12 +2185,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2200,19 +2210,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>bene/fra</t>
+          <t>fra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11:08 volpe e bo/images@bene -&gt; 11:23 tappeto/text@fra</t>
+          <t>11:27 gatta/images@fra -&gt; 11:35 sbadiglio/text@fra</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I39" t="n">
-        <v>90</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="J39" t="n">
         <v>2</v>
@@ -2221,12 +2231,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F14</t>
+          <t>F15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2251,14 +2261,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11:27 gatta/images@fra -&gt; 11:35 sbadiglio/text@fra</t>
+          <t>11:32 delfino/images@fra -&gt; 11:39 panda/text@fra</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>60</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="I40" t="n">
-        <v>83.33333333333334</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="J40" t="n">
         <v>2</v>
@@ -2267,7 +2277,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F15</t>
+          <t>F16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2292,19 +2302,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>fra</t>
+          <t>bene</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11:32 delfino/images@fra -&gt; 11:39 panda/text@fra</t>
+          <t>11:43 delfino/images@bene -&gt; 11:51 panda/text@bene</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>42.85714285714285</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="I41" t="n">
-        <v>78.57142857142857</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
@@ -2313,12 +2323,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2338,19 +2348,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>bene</t>
+          <t>bene/fra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11:43 delfino/images@bene -&gt; 11:51 panda/text@bene</t>
+          <t>11:47 volpe e bo/images@bene -&gt; 11:51 tappeto/text@fra</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>64.28571428571429</v>
+        <v>90</v>
       </c>
       <c r="I42" t="n">
-        <v>64.28571428571429</v>
+        <v>50</v>
       </c>
       <c r="J42" t="n">
         <v>2</v>
@@ -2359,12 +2369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F17</t>
+          <t>F18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2384,19 +2394,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>bene/fra</t>
+          <t>fra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11:47 volpe e bo/images@bene -&gt; 11:51 tappeto/text@fra</t>
+          <t>11:49 volpe e bo/images@fra -&gt; 11:56 tappeto/text@fra</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J43" t="n">
         <v>2</v>
@@ -2405,12 +2415,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F18</t>
+          <t>F20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2425,24 +2435,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>mattina</t>
+          <t>pomeriggio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>fra</t>
+          <t>fra/bene</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11:49 volpe e bo/images@fra -&gt; 11:56 tappeto/text@fra</t>
+          <t>13:56 volpe e bo/images@fra -&gt; 14:06 tappeto/text@bene</t>
         </is>
       </c>
       <c r="H44" t="n">
+        <v>80</v>
+      </c>
+      <c r="I44" t="n">
         <v>100</v>
-      </c>
-      <c r="I44" t="n">
-        <v>80</v>
       </c>
       <c r="J44" t="n">
         <v>2</v>
@@ -2451,12 +2461,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F20</t>
+          <t>F21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2476,19 +2486,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>fra/bene</t>
+          <t>fra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>13:56 volpe e bo/images@fra -&gt; 14:06 tappeto/text@bene</t>
+          <t>13:59 volpe e bo/images@fra -&gt; 14:06 tappeto/text@fra</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J45" t="n">
         <v>2</v>
@@ -2497,12 +2507,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>F21</t>
+          <t>F22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2522,19 +2532,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>fra</t>
+          <t>fra/bene</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13:59 volpe e bo/images@fra -&gt; 14:06 tappeto/text@fra</t>
+          <t>14:15 anguille/images@fra -&gt; 14:23 orso/text@bene</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>40</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="I46" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
@@ -2543,12 +2553,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F22</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2573,14 +2583,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14:15 anguille/images@fra -&gt; 14:23 orso/text@bene</t>
+          <t>14:22 volpe e bo/images@fra -&gt; 14:31 tappeto/text@bene</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J47" t="n">
         <v>2</v>
@@ -2589,7 +2599,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F23</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2614,118 +2624,118 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>fra/bene</t>
+          <t>fra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14:22 volpe e bo/images@fra -&gt; 14:31 tappeto/text@bene</t>
+          <t>14:26 volpe e bo/images@fra -&gt; 14:34 tappeto/text@fra</t>
         </is>
       </c>
       <c r="H48" t="n">
+        <v>90</v>
+      </c>
+      <c r="I48" t="n">
+        <v>40</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>F25</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>IT?</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>presunto (1 gaze mancante)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>pomeriggio</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>fra</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>14:30 volpe e bo/images@fra</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>pomeriggio</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>fra</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>14:40 volpe e bo/images@fra -&gt; 14:45 tappeto/text@fra</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>70</v>
+      </c>
+      <c r="I50" t="n">
         <v>100</v>
       </c>
-      <c r="I48" t="n">
-        <v>80</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>F24</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>pomeriggio</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>fra</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>14:26 volpe e bo/images@fra -&gt; 14:34 tappeto/text@fra</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>90</v>
-      </c>
-      <c r="I49" t="n">
-        <v>40</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>F25</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>IT?</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>presunto (1 gaze mancante)</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>pomeriggio</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>fra</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>14:30 volpe e bo/images@fra</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>1</v>
+      <c r="J50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2750,19 +2760,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>fra</t>
+          <t>fra/bene</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14:40 volpe e bo/images@fra -&gt; 14:45 tappeto/text@fra</t>
+          <t>14:50 volpe e bo/images@fra -&gt; 15:04 tappeto/text@bene</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J51" t="n">
         <v>2</v>
@@ -2771,7 +2781,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F31</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2796,19 +2806,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>fra/bene</t>
+          <t>bene/fra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14:50 volpe e bo/images@fra -&gt; 15:04 tappeto/text@bene</t>
+          <t>14:55 volpe e bo/images@bene -&gt; 15:03 tappeto/text@fra</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I52" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J52" t="n">
         <v>2</v>
@@ -2817,7 +2827,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F32</t>
+          <t>F33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2842,118 +2852,118 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>bene/fra</t>
+          <t>bene</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14:55 volpe e bo/images@bene -&gt; 15:03 tappeto/text@fra</t>
+          <t>15:13 volpe e bo/images@bene -&gt; 15:18 tappeto/text@bene</t>
         </is>
       </c>
       <c r="H53" t="n">
+        <v>60</v>
+      </c>
+      <c r="I53" t="n">
         <v>90</v>
       </c>
-      <c r="I53" t="n">
-        <v>60</v>
-      </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>F33</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>ANOMALO (TT)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>pomeriggio</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>bene</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>15:15 volpe e bo/text@bene -&gt; 15:22 tappeto/text@bene</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F40</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>pomeriggio</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>bene</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>15:13 volpe e bo/images@bene -&gt; 15:18 tappeto/text@bene</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>60</v>
-      </c>
-      <c r="I54" t="n">
-        <v>90</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>F35</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>ANOMALO (TT)</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>pomeriggio</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>bene</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>15:15 volpe e bo/text@bene -&gt; 15:22 tappeto/text@bene</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="n">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>fra</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>14:54 volpe e bo/images@fra -&gt; 15:00 tappeto/text@fra</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>100</v>
+      </c>
+      <c r="I55" t="n">
+        <v>40</v>
+      </c>
+      <c r="J55" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F40</t>
+          <t>F41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2983,62 +2993,16 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14:54 volpe e bo/images@fra -&gt; 15:00 tappeto/text@fra</t>
+          <t>15:11 volpe e bo/images@fra -&gt; 15:17 tappeto/text@fra</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I56" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>F41</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>pomeriggio</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>fra</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>15:11 volpe e bo/images@fra -&gt; 15:17 tappeto/text@fra</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>80</v>
-      </c>
-      <c r="I57" t="n">
-        <v>60</v>
-      </c>
-      <c r="J57" t="n">
         <v>2</v>
       </c>
     </row>
